--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.860257988317704</v>
+        <v>1.602291923101627</v>
       </c>
       <c r="D2" t="n">
-        <v>10.26670244057324</v>
+        <v>1.668339146593151</v>
       </c>
       <c r="E2" t="n">
-        <v>5.34202517566322</v>
+        <v>0.8680790910452734</v>
       </c>
       <c r="F2" t="n">
-        <v>4.005835351250476</v>
+        <v>0.6509482445782022</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.403563268859321</v>
+        <v>1.20307903118964</v>
       </c>
       <c r="D3" t="n">
-        <v>5.788798889736073</v>
+        <v>0.9406798195821119</v>
       </c>
       <c r="E3" t="n">
-        <v>5.34202517566322</v>
+        <v>0.8680790910452734</v>
       </c>
       <c r="F3" t="n">
-        <v>4.005835351250476</v>
+        <v>0.6509482445782022</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.66493587861673</v>
+        <v>2.383052080275218</v>
       </c>
       <c r="D4" t="n">
-        <v>13.35010059544123</v>
+        <v>2.169391346759199</v>
       </c>
       <c r="E4" t="n">
-        <v>5.34202517566322</v>
+        <v>0.8680790910452734</v>
       </c>
       <c r="F4" t="n">
-        <v>4.005835351250476</v>
+        <v>0.6509482445782022</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.585758190179456</v>
+        <v>0.4201857059041616</v>
       </c>
       <c r="D5" t="n">
-        <v>4.920276809816635</v>
+        <v>0.7995449815952032</v>
       </c>
       <c r="E5" t="n">
-        <v>5.34202517566322</v>
+        <v>0.8680790910452734</v>
       </c>
       <c r="F5" t="n">
-        <v>4.005835351250476</v>
+        <v>0.6509482445782022</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.760659035643</v>
+        <v>2.886107093291987</v>
       </c>
       <c r="D6" t="n">
-        <v>15.04776602203565</v>
+        <v>2.445261978580793</v>
       </c>
       <c r="E6" t="n">
-        <v>5.34202517566322</v>
+        <v>0.8680790910452734</v>
       </c>
       <c r="F6" t="n">
-        <v>4.005835351250476</v>
+        <v>0.6509482445782022</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
